--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Trend_Method_Comparison_All_vs_MK.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Trend_Method_Comparison_All_vs_MK.xlsx
@@ -13348,7 +13348,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.0984</v>
+        <v>2.7251</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
